--- a/output/laminas_comunales/comunal_i_peringr_median_a_2019_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2019_atacama.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,11 +588,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,28 +595,19 @@
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="B2">
-        <v>20.36</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caldera</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>12</v>
+          <t>Freirina</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chañaral</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>10.61</v>
+          <t>Huasco</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -630,48 +616,33 @@
           <t>Copiapó</t>
         </is>
       </c>
-      <c r="B5">
-        <v>11.7</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>7.47</v>
+          <t>Caldera</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Freirina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>14.34</v>
+          <t>Chañaral</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Huasco</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>12.04</v>
+          <t>Tierra Amarilla</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>17.68</v>
+          <t>Diego de Almagro</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -679,9 +650,6 @@
         <is>
           <t>Vallenar</t>
         </is>
-      </c>
-      <c r="B10">
-        <v>11.76</v>
       </c>
     </row>
   </sheetData>
